--- a/2604/0428.xlsx
+++ b/2604/0428.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="131">
   <si>
     <t>相川様の方向性（方式①をベースにすること）には賛同いたします。</t>
   </si>
@@ -442,6 +443,116 @@
   </si>
   <si>
     <t>フルフローを検証させていただけないでしょうか。</t>
+  </si>
+  <si>
+    <t>这份回复为你专门定制了。开头先诚恳地道了歉（承认上一次在时间轴和具体流程上没有讲明白），紧接着单刀直入地回答他的两个核心疑问，最后抛出我们刚刚理清的**“事前建空壳，发布塞镜像”**的杀手锏逻辑。</t>
+  </si>
+  <si>
+    <t>你不仅能完美化解他的担忧，还能展现出你对系统架构解耦的深刻理解。</t>
+  </si>
+  <si>
+    <t>你可以直接复制以下日文发到群里：</t>
+  </si>
+  <si>
+    <t>***</t>
+  </si>
+  <si>
+    <t>**@富田 哲夫** さん</t>
+  </si>
+  <si>
+    <t>ご確認ありがとうございます。</t>
+  </si>
+  <si>
+    <t>前回の私の記載で、具体的な実現フロー（特に実行タイミングとパイプラインの切り分け）について明確な説明が不足しており、大変申し訳ありません。非常に重要なポイントをご指摘いただきありがとうございます。</t>
+  </si>
+  <si>
+    <t>ご懸念の通り、ECS Service（例：`splitter-v1a54`）の新規作成などの「重いインフラ構築」をリリース作業（ダウンタイム）中に含めてしまうと、AWS側の構築待ち時間が発生し「リリース時間の短縮」という目的に完全に逆行してしまいます。</t>
+  </si>
+  <si>
+    <t>そのため、ご質問いただいた点については、**パイプラインと実行タイミングを完全に分離する**想定で考えておりました。</t>
+  </si>
+  <si>
+    <t>**1. どのパイプラインで作成するか？**</t>
+  </si>
+  <si>
+    <r>
+      <t>アプリのビルド</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>デプロイを行うCICDパイプライン（アプリ用）とは別の、**インフラ構築用のパイプライン（CloudFormation/CDK実行用）**で作成します。</t>
+    </r>
+  </si>
+  <si>
+    <t>**2. それはリリース時か？**</t>
+  </si>
+  <si>
+    <t>**いいえ、リリース時（デプロイの作業枠内）ではありません。リリース前の「事前準備」として実行します。**</t>
+  </si>
+  <si>
+    <t>具体的なタイムラインのイメージは以下の通りです。</t>
+  </si>
+  <si>
+    <t>**【フェーズ①：事前準備（リリース前）】** ※リリース時間（ダウンタイム）には影響しません</t>
+  </si>
+  <si>
+    <t>* インフラ用のパイプラインを実行し、待機系となる新しい全体バージョンのリソース（`ECS Service: splitter-v1a54` やMQ、ALB Target Groupなど）を先行して作成しておきます。</t>
+  </si>
+  <si>
+    <t>* （※この時点では、ECS Serviceのタスク数（Desired Count）を0にしておくなど、インフラの「空枠」だけを事前に用意しておくイメージです。）</t>
+  </si>
+  <si>
+    <t>**【フェーズ②：リリース実行（リリース時）】** ※ここで時間を極小化します</t>
+  </si>
+  <si>
+    <t>* アプリ用のCICDパイプラインを実行します。</t>
+  </si>
+  <si>
+    <t>* 変更のあったコンポーネントのみイメージビルド（変更なしは再利用）を行い、新しいTask Definition（タスク定義）を登録します。</t>
+  </si>
+  <si>
+    <t>* **事前作成済みのECS Service（splitter-v1a54）**に対して、このタスク定義を紐づけてタスクを起動し、Blue/Greenの流量切り替えのみを行います。</t>
+  </si>
+  <si>
+    <t>このように、「時間のかかるインフラリソース作成は事前」「時間のかからないコンテナ更新と切り替えのみリリース時」と分けることで、リリース時間の短縮が実現できると考えております。</t>
+  </si>
+  <si>
+    <t>こちらの想定で、富田さんのご懸念は解消されますでしょうか？</t>
+  </si>
+  <si>
+    <t>ご見解をお伺いできますと幸いです。よろしくお願いいたします。</t>
+  </si>
+  <si>
+    <t>### 💡 这段回复的精妙之处：</t>
+  </si>
+  <si>
+    <t>1. **“大変申し訳ありません” + “非常に重要なポイント”**：先放低姿态道歉，然后把富田捧高（肯定他的担忧非常专业且直击要害）。技术大佬最吃这一套。</t>
+  </si>
+  <si>
+    <t>2. **“完全に逆行してしまいます”**：用了很坚定的词，表示你完全同意他“发布时间不能变长”的核心底线，大家是在同一条战线上的。</t>
+  </si>
+  <si>
+    <t>3. **引入“フェーズ（Phase/阶段）”的概念**：清晰地把【事前建空枠（空壳）】和【发布时切流量】分开，彻底解开了他心中“你要在发布当晚建基础设施”的误会。</t>
+  </si>
+  <si>
+    <t>发出去之后，可以观察一下富田的反应。如果他同意，那么恭喜你，你已经主导了这次架构方向的制定！</t>
   </si>
 </sst>
 </file>
@@ -1318,5 +1429,167 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:A47"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/2604/0428.xlsx
+++ b/2604/0428.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="172">
   <si>
     <t>相川様の方向性（方式①をベースにすること）には賛同いたします。</t>
   </si>
@@ -553,6 +554,326 @@
   </si>
   <si>
     <t>发出去之后，可以观察一下富田的反应。如果他同意，那么恭喜你，你已经主导了这次架构方向的制定！</t>
+  </si>
+  <si>
+    <t>以下是为您翻译的日文版本，已按照日本职场沟通习惯调整了措辞与格式，可直接复制使用：</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>@相川 大輔 様</t>
+  </si>
+  <si>
+    <t>ご確認いただき、また案Cでの推進をご決断いただき、誠にありがとうございます。</t>
+  </si>
+  <si>
+    <t>開発環境での空デプロイの件、大変助かります。現状のデプロイフローやCDKの仕様を正確に把握するため、徐さんのサポートをいただきながら進めさせていただきます。</t>
+  </si>
+  <si>
+    <t>この後の進め方とWBSの再整理について、以下の通り回答いたします。</t>
+  </si>
+  <si>
+    <t>**1. PoCの実施意向について**</t>
+  </si>
+  <si>
+    <r>
+      <t>はい、おっしゃる通り、いきなりCDKの正式な設計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>改修に入るのではなく、まずはPoC（概念検証）を実施したいと考えております。</t>
+    </r>
+  </si>
+  <si>
+    <t>CDK側のみで案Cの仕組みが開発環境において想定通りに動作するか検証し、メカニズムの有効性を確認いたします。</t>
+  </si>
+  <si>
+    <t>**2. WBSの再整理（消滅タスクと追加タスク）について**</t>
+  </si>
+  <si>
+    <t>現時点で明確になっているタスクの増減は以下の通りです。</t>
+  </si>
+  <si>
+    <t>**【消滅するタスク】**</t>
+  </si>
+  <si>
+    <r>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>課題3への対応タスク（先日検証した通り、現状でMQの物理隔離が担保されているため、当該課題自体が不要となりました）</t>
+    </r>
+  </si>
+  <si>
+    <t>**【追加となるタスク（大枠）】**</t>
+  </si>
+  <si>
+    <r>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>現状デプロイフローの把握（徐さんとの空デプロイ実施を含む） 1人日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CDK設計書およびソースコードの確認 2.5人日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>バージョンマニフェスト（管理表）の設計 1人日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>案Cの仕組みを検証するためのPoC実施 5人日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PoC成功後のCDK改修設計 2人日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PoC成功後のCDK改修実装 2.5人日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>※現在、インフラ部分への調査がまだ深まっていないため、上記は大まかなタスク想定となります。進捗に伴い新たな判明事項があれば、随時相川様へご報告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>共有させていただきます。</t>
+    </r>
+  </si>
+  <si>
+    <t>以上、よろしくお願いいたします。</t>
+  </si>
+  <si>
+    <t>💡 **翻译说明**：</t>
+  </si>
+  <si>
+    <t>- `1人/日` 已统一调整为日本项目管理常用表述 `1人日`</t>
+  </si>
+  <si>
+    <t>- `空部署` 沿用前文语境译为 `空デプロイ`（指不触达实际业务逻辑的流水线空跑/干跑测试）</t>
+  </si>
+  <si>
+    <t>=================================</t>
+  </si>
+  <si>
+    <t>**@相川 大輔** さん</t>
+  </si>
+  <si>
+    <t>ご確認および案Cでの推進をご決断いただき、ありがとうございます。</t>
+  </si>
+  <si>
+    <t>開発環境での空デプロイの件、大変助かります。現状のデプロイフローとCDKの仕様を正確に把握するため、徐さんのサポートをいただきながら進めさせていただきます。</t>
+  </si>
+  <si>
+    <t>**1. PoCの意向について**</t>
+  </si>
+  <si>
+    <r>
+      <t>はい、おっしゃる通り、いきなりCDKの正式な設計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>改修に入るのではなく、**まずはPoC（概念検証</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>デモの作成）を挟みたい**と考えております。</t>
+    </r>
+  </si>
+  <si>
+    <t>業務コードは変更せず、インフラ（CDK）側だけで「差分デプロイ」や「Task Definitionのみの更新」が現在の環境で想定通り動作するか、仕組みを検証いたします。</t>
+  </si>
+  <si>
+    <t>*   **【消滅するタスク】**：課題３への対応タスク（先日検証した通り、現状でMQの物理隔離が担保されているため課題自体が消滅しました）</t>
+  </si>
+  <si>
+    <t>*   **【追加となるタスク（大枠）】**：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    *   現状デプロイフローの把握と設計書の確認（徐さんとの空デプロイ実施を含む）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    *   バージョンマニフェスト（管理表）の設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    *   案Cの仕組みを検証するためのPoC実施</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    *   PoC完了後のCDK改修設計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>実装</t>
+    </r>
+  </si>
+  <si>
+    <t>より具体的で精緻なWBS（各タスクの工数や詳細な作業内容）につきましては、**私が現在のCDKのソースコードやリリース現状を正確に把握した上で提示すべき**と考えております。</t>
+  </si>
+  <si>
+    <t>そのため、まずは「現状把握（徐さんとの空デプロイや設計書の確認）」を先行させていただき、その結果をもとに、詳細なWBSをご提示するという進め方でよろしいでしょうか？</t>
+  </si>
+  <si>
+    <t>よろしくお願いいたします。</t>
   </si>
 </sst>
 </file>
@@ -1591,5 +1912,258 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A71"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" t="e">
+        <f>- 语气保持了日企沟通中常见的「谦逊+明确」风格,便于领导快速审批与安排资源</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>156</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>